--- a/Result/profitability/1786.xlsx
+++ b/Result/profitability/1786.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM70"/>
+  <dimension ref="A1:AM71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>-1.42</v>
       </c>
       <c r="M2" t="n">
-        <v>0.36125</v>
+        <v>0.3175</v>
       </c>
       <c r="N2" t="n">
-        <v>56.345</v>
+        <v>55.56125</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>-1.38</v>
       </c>
       <c r="M3" t="n">
-        <v>0.08625000000000005</v>
+        <v>0.02625000000000002</v>
       </c>
       <c r="N3" t="n">
-        <v>46.91875</v>
+        <v>45.8725</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>-0.96</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1525</v>
+        <v>-0.1924999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>2.399999999999999</v>
+        <v>1.938750000000006</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.71</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.34</v>
+        <v>-0.25375</v>
       </c>
       <c r="N5" t="n">
-        <v>-9.641249999999999</v>
+        <v>-10.52124999999999</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.41</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.3637499999999999</v>
+        <v>-0.4062499999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>-23.02</v>
+        <v>-23.48249999999999</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>-0.08</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.475</v>
+        <v>-0.5249999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>-29.5725</v>
+        <v>-30.75125</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>-0.21</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.61</v>
+        <v>-0.5874999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>-34.3875</v>
+        <v>-34.99124999999999</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1521,7 +1521,7 @@
         <v>-0.5875</v>
       </c>
       <c r="N9" t="n">
-        <v>-36.52125</v>
+        <v>-36.52124999999999</v>
       </c>
       <c r="O9" t="n">
         <v>1</v>
@@ -9318,6 +9318,133 @@
       </c>
       <c r="AM70" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>1786</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>211</v>
+      </c>
+      <c r="D71" t="n">
+        <v>72</v>
+      </c>
+      <c r="E71" t="n">
+        <v>139</v>
+      </c>
+      <c r="F71" t="n">
+        <v>65.89</v>
+      </c>
+      <c r="G71" t="n">
+        <v>29</v>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>13.61%</t>
+        </is>
+      </c>
+      <c r="I71" t="n">
+        <v>-1</v>
+      </c>
+      <c r="J71" t="n">
+        <v>28</v>
+      </c>
+      <c r="K71" t="n">
+        <v>35</v>
+      </c>
+      <c r="L71" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="M71" t="n">
+        <v>0.5975</v>
+      </c>
+      <c r="N71" t="n">
+        <v>71.30625000000001</v>
+      </c>
+      <c r="O71" t="n">
+        <v>0</v>
+      </c>
+      <c r="P71" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q71" t="n">
+        <v>0</v>
+      </c>
+      <c r="R71" t="n">
+        <v>0</v>
+      </c>
+      <c r="S71" t="n">
+        <v>0</v>
+      </c>
+      <c r="T71" t="n">
+        <v>0</v>
+      </c>
+      <c r="U71" t="n">
+        <v>0</v>
+      </c>
+      <c r="V71" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W71" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="X71" t="n">
+        <v>0.6206896551724139</v>
+      </c>
+      <c r="Y71" t="n">
+        <v>-4.829999999999998</v>
+      </c>
+      <c r="Z71" t="n">
+        <v>-0.06829751131221717</v>
+      </c>
+      <c r="AA71" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="AB71" t="n">
+        <v>-3.136363636363636</v>
+      </c>
+      <c r="AC71" t="n">
+        <v>-7.040000000000006</v>
+      </c>
+      <c r="AD71" t="n">
+        <v>-0.09653092006033193</v>
+      </c>
+      <c r="AE71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF71" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI71" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ71" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK71" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL71" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM71" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
